--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-09-2025.xlsx
@@ -815,7 +815,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£16.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>£37.39</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
